--- a/Retry的thread.sleep方式比較.xlsx
+++ b/Retry的thread.sleep方式比較.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C_PLUS_PLUS\OneDrive - 國立宜蘭大學\桌面\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C_PLUS_PLUS\OneDrive - 國立宜蘭大學\桌面\coupon-demo\coupon-demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC3D170-EAA3-4BA3-BFDB-079F5EB7B657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5D7D44-5317-4813-8D76-DE9DF51339EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{608F7201-E434-4565-92F7-6AD10B08AB5F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t>baseDelay + retryTime * stepDelay + jitter;</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,12 +88,31 @@
     <t>99%_latency</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>CONFLICT_TRY_AGAIN/issue</t>
+  </si>
+  <si>
+    <t>CONFLICT_TRY_AGAIN/issue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500request</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100request</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50request</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -115,6 +134,14 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -133,21 +160,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -479,30 +513,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E760EE22-905B-4C7A-BF40-C9153EAABE56}">
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="31.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="25.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="39.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="12" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.453125" customWidth="1"/>
+    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="39.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="31.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A1" s="1"/>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B1" t="s">
         <v>6</v>
       </c>
@@ -510,64 +550,73 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>4</v>
       </c>
       <c r="M1" s="1"/>
       <c r="N1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" t="s">
         <v>6</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>5</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>2</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>3</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>50</v>
@@ -575,251 +624,283 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
+        <f>C2/50</f>
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>28</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>15</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>216</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>23</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>33</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>38</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>216</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>50</v>
       </c>
-      <c r="M2" t="s">
-        <v>0</v>
-      </c>
-      <c r="N2">
+      <c r="N2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2">
         <v>50</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
       <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2">
+        <f>P2/50</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
         <v>43</v>
       </c>
-      <c r="Q2">
+      <c r="S2">
         <v>16</v>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>301</v>
       </c>
-      <c r="S2">
+      <c r="U2">
         <v>24</v>
       </c>
-      <c r="T2">
+      <c r="V2">
         <v>106</v>
       </c>
-      <c r="U2">
+      <c r="W2">
         <v>164</v>
       </c>
-      <c r="V2">
+      <c r="X2">
         <v>301</v>
       </c>
-      <c r="W2">
+      <c r="Y2">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.4">
       <c r="B3">
         <v>49</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
+        <f t="shared" ref="D3:D21" si="0">C3/50</f>
+        <v>0.02</v>
+      </c>
+      <c r="E3">
         <v>40</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>14</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>283</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>22</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>93</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>114</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>283</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>50</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>49</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>1</v>
       </c>
-      <c r="P3">
+      <c r="Q3" s="2">
+        <f t="shared" ref="Q3:Q7" si="1">P3/50</f>
+        <v>0.02</v>
+      </c>
+      <c r="R3">
         <v>37</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>15</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>309</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <v>23</v>
       </c>
-      <c r="T3">
+      <c r="V3">
         <v>60</v>
       </c>
-      <c r="U3">
+      <c r="W3">
         <v>87</v>
       </c>
-      <c r="V3">
+      <c r="X3">
         <v>309</v>
       </c>
-      <c r="W3">
+      <c r="Y3">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.4">
       <c r="B4">
         <v>50</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>23</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>15</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>96</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>20</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>34</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>40</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>96</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>50</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>50</v>
       </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
       <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R4">
         <v>18</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>12</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>26</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>18</v>
       </c>
-      <c r="T4">
+      <c r="V4">
         <v>21</v>
       </c>
-      <c r="U4">
+      <c r="W4">
         <v>21</v>
       </c>
-      <c r="V4">
+      <c r="X4">
         <v>26</v>
       </c>
-      <c r="W4">
+      <c r="Y4">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.4">
       <c r="B5">
         <v>50</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>18</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>12</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>34</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>18</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>21</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>23</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>34</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>50</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>50</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
       <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R5">
         <v>47</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>16</v>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>271</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>21</v>
       </c>
-      <c r="T5">
+      <c r="V5">
         <v>145</v>
       </c>
-      <c r="U5">
+      <c r="W5">
         <v>186</v>
       </c>
-      <c r="V5">
+      <c r="X5">
         <v>271</v>
       </c>
-      <c r="W5">
+      <c r="Y5">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
       <c r="B6">
         <v>50</v>
@@ -827,937 +908,1069 @@
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>16</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>11</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>31</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>16</v>
-      </c>
-      <c r="H6">
-        <v>20</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6">
         <v>31</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>50</v>
       </c>
       <c r="M6" s="1"/>
-      <c r="N6">
+      <c r="N6" s="1"/>
+      <c r="O6">
         <v>50</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
       <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R6">
         <v>18</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <v>12</v>
       </c>
-      <c r="R6">
+      <c r="T6">
         <v>25</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <v>18</v>
       </c>
-      <c r="T6">
+      <c r="V6">
         <v>20</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <v>21</v>
       </c>
-      <c r="V6">
+      <c r="X6">
         <v>25</v>
       </c>
-      <c r="W6">
+      <c r="Y6">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7">
-        <f>SUM(B2:B6)/5</f>
+        <f t="shared" ref="B7:J7" si="2">SUM(B2:B6)/5</f>
         <v>49.8</v>
       </c>
       <c r="C7">
-        <f>SUM(C2:C6)/5</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
-      <c r="D7">
-        <f>SUM(D2:D6)/5</f>
+      <c r="D7" s="2">
+        <f t="shared" si="0"/>
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E7">
+        <f t="shared" ref="E7" si="3">SUM(E2:E6)/5</f>
         <v>25</v>
       </c>
-      <c r="E7">
-        <f>SUM(E2:E6)/5</f>
+      <c r="F7">
+        <f t="shared" ref="F7" si="4">SUM(F2:F6)/5</f>
         <v>13.4</v>
       </c>
-      <c r="F7">
-        <f>SUM(F2:F6)/5</f>
+      <c r="G7">
+        <f t="shared" ref="G7" si="5">SUM(G2:G6)/5</f>
         <v>132</v>
       </c>
-      <c r="G7">
-        <f>SUM(G2:G6)/5</f>
+      <c r="H7">
+        <f t="shared" ref="H7" si="6">SUM(H2:H6)/5</f>
         <v>19.8</v>
       </c>
-      <c r="H7">
-        <f>SUM(H2:H6)/5</f>
+      <c r="I7">
+        <f t="shared" ref="I7" si="7">SUM(I2:I6)/5</f>
         <v>40.200000000000003</v>
       </c>
-      <c r="I7">
-        <f>SUM(I2:I6)/5</f>
+      <c r="J7">
+        <f t="shared" ref="J7" si="8">SUM(J2:J6)/5</f>
         <v>47</v>
       </c>
-      <c r="J7">
-        <f>SUM(J2:J6)/5</f>
+      <c r="K7">
+        <f t="shared" ref="K7" si="9">SUM(K2:K6)/5</f>
         <v>132</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>50</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>8</v>
       </c>
-      <c r="N7">
-        <f>SUM(N2:N6)/5</f>
+      <c r="O7">
+        <f t="shared" ref="O7" si="10">SUM(O2:O6)/5</f>
         <v>49.8</v>
       </c>
-      <c r="O7">
-        <f>SUM(O2:O6)/5</f>
+      <c r="P7">
+        <f t="shared" ref="P7" si="11">SUM(P2:P6)/5</f>
         <v>0.2</v>
       </c>
-      <c r="P7">
-        <f>SUM(P2:P6)/5</f>
+      <c r="Q7" s="2">
+        <f t="shared" si="1"/>
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="R7">
+        <f t="shared" ref="R7" si="12">SUM(R2:R6)/5</f>
         <v>32.6</v>
       </c>
-      <c r="Q7">
-        <f>SUM(Q2:Q6)/5</f>
+      <c r="S7">
+        <f t="shared" ref="S7" si="13">SUM(S2:S6)/5</f>
         <v>14.2</v>
       </c>
-      <c r="R7">
-        <f>SUM(R2:R6)/5</f>
+      <c r="T7">
+        <f t="shared" ref="T7" si="14">SUM(T2:T6)/5</f>
         <v>186.4</v>
       </c>
-      <c r="S7">
-        <f>SUM(S2:S6)/5</f>
+      <c r="U7">
+        <f t="shared" ref="U7" si="15">SUM(U2:U6)/5</f>
         <v>20.8</v>
       </c>
-      <c r="T7">
-        <f>SUM(T2:T6)/5</f>
+      <c r="V7">
+        <f t="shared" ref="V7" si="16">SUM(V2:V6)/5</f>
         <v>70.400000000000006</v>
       </c>
-      <c r="U7">
-        <f>SUM(U2:U6)/5</f>
+      <c r="W7">
+        <f t="shared" ref="W7" si="17">SUM(W2:W6)/5</f>
         <v>95.8</v>
       </c>
-      <c r="V7">
-        <f>SUM(V2:V6)/5</f>
+      <c r="X7">
+        <f t="shared" ref="X7" si="18">SUM(X2:X6)/5</f>
         <v>186.4</v>
       </c>
-      <c r="W7">
+      <c r="Y7">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
       <c r="B9">
         <v>96</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
+        <f>C9/100</f>
+        <v>0.04</v>
+      </c>
+      <c r="E9">
         <v>55</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>10</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>302</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>16</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>177</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>210</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>268</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>100</v>
       </c>
-      <c r="N9">
-        <v>92</v>
+      <c r="N9" t="s">
+        <v>16</v>
       </c>
       <c r="O9">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2">
+        <f>P9/50</f>
+        <v>0.02</v>
+      </c>
+      <c r="R9">
         <v>167</v>
       </c>
-      <c r="Q9">
+      <c r="S9">
         <v>14</v>
       </c>
-      <c r="R9">
+      <c r="T9">
         <v>410</v>
       </c>
-      <c r="S9">
+      <c r="U9">
         <v>144</v>
       </c>
-      <c r="T9">
+      <c r="V9">
         <v>468</v>
       </c>
-      <c r="U9">
+      <c r="W9">
         <v>509</v>
       </c>
-      <c r="V9">
+      <c r="X9">
         <v>567</v>
       </c>
-      <c r="W9">
+      <c r="Y9">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.4">
       <c r="B10">
         <v>100</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
+        <f t="shared" ref="D10:D14" si="19">C10/100</f>
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>15</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>8</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>100</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>14</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>18</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>22</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>83</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>100</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>99</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>1</v>
       </c>
-      <c r="P10">
+      <c r="Q10" s="2">
+        <f t="shared" ref="Q10:Q14" si="20">P10/50</f>
+        <v>0.02</v>
+      </c>
+      <c r="R10">
         <v>28</v>
       </c>
-      <c r="Q10">
+      <c r="S10">
         <v>11</v>
       </c>
-      <c r="R10">
+      <c r="T10">
         <v>300</v>
       </c>
-      <c r="S10">
+      <c r="U10">
         <v>17</v>
       </c>
-      <c r="T10">
+      <c r="V10">
         <v>41</v>
       </c>
-      <c r="U10">
+      <c r="W10">
         <v>116</v>
       </c>
-      <c r="V10">
+      <c r="X10">
         <v>127</v>
       </c>
-      <c r="W10">
+      <c r="Y10">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.4">
       <c r="B11">
         <v>100</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>10</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>5</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>28</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>10</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>15</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>16</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>23</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>100</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>100</v>
       </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
       <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R11">
         <v>17</v>
       </c>
-      <c r="Q11">
+      <c r="S11">
         <v>11</v>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>123</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>14</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>21</v>
       </c>
-      <c r="U11">
+      <c r="W11">
         <v>33</v>
       </c>
-      <c r="V11">
+      <c r="X11">
         <v>45</v>
       </c>
-      <c r="W11">
+      <c r="Y11">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.4">
       <c r="B12">
         <v>99</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
+        <f t="shared" si="19"/>
+        <v>0.01</v>
+      </c>
+      <c r="E12">
         <v>17</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>8</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>227</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>13</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>22</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>27</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>93</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>100</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>100</v>
       </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
       <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R12">
         <v>18</v>
       </c>
-      <c r="Q12">
+      <c r="S12">
         <v>9</v>
       </c>
-      <c r="R12">
+      <c r="T12">
         <v>268</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>14</v>
       </c>
-      <c r="T12">
+      <c r="V12">
         <v>18</v>
       </c>
-      <c r="U12">
+      <c r="W12">
         <v>24</v>
       </c>
-      <c r="V12">
+      <c r="X12">
         <v>129</v>
       </c>
-      <c r="W12">
+      <c r="Y12">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.4">
       <c r="B13">
         <v>100</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="E13">
         <v>12</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>8</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>77</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>12</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>15</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>18</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>26</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>100</v>
       </c>
-      <c r="N13">
-        <v>92</v>
-      </c>
       <c r="O13">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R13">
         <v>81</v>
       </c>
-      <c r="Q13">
+      <c r="S13">
         <v>9</v>
       </c>
-      <c r="R13">
+      <c r="T13">
         <v>447</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>18</v>
       </c>
-      <c r="T13">
+      <c r="V13">
         <v>227</v>
       </c>
-      <c r="U13">
+      <c r="W13">
         <v>298</v>
       </c>
-      <c r="V13">
+      <c r="X13">
         <v>409</v>
       </c>
-      <c r="W13">
+      <c r="Y13">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>8</v>
       </c>
       <c r="B14">
-        <f>SUM(B9:B13)/5</f>
+        <f t="shared" ref="B14:J14" si="21">SUM(B9:B13)/5</f>
         <v>99</v>
       </c>
       <c r="C14">
-        <f>SUM(C9:C13)/5</f>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
-      <c r="D14">
-        <f>SUM(D9:D13)/5</f>
+      <c r="D14" s="2">
+        <f t="shared" si="19"/>
+        <v>0.01</v>
+      </c>
+      <c r="E14">
+        <f t="shared" ref="E14" si="22">SUM(E9:E13)/5</f>
         <v>21.8</v>
       </c>
-      <c r="E14">
-        <f>SUM(E9:E13)/5</f>
+      <c r="F14">
+        <f t="shared" ref="F14" si="23">SUM(F9:F13)/5</f>
         <v>7.8</v>
       </c>
-      <c r="F14">
-        <f>SUM(F9:F13)/5</f>
+      <c r="G14">
+        <f t="shared" ref="G14" si="24">SUM(G9:G13)/5</f>
         <v>146.80000000000001</v>
       </c>
-      <c r="G14">
-        <f>SUM(G9:G13)/5</f>
+      <c r="H14">
+        <f t="shared" ref="H14" si="25">SUM(H9:H13)/5</f>
         <v>13</v>
       </c>
-      <c r="H14">
-        <f>SUM(H9:H13)/5</f>
+      <c r="I14">
+        <f t="shared" ref="I14" si="26">SUM(I9:I13)/5</f>
         <v>49.4</v>
       </c>
-      <c r="I14">
-        <f>SUM(I9:I13)/5</f>
+      <c r="J14">
+        <f t="shared" ref="J14" si="27">SUM(J9:J13)/5</f>
         <v>58.6</v>
       </c>
-      <c r="J14">
-        <f>SUM(J9:J13)/5</f>
+      <c r="K14">
+        <f t="shared" ref="K14" si="28">SUM(K9:K13)/5</f>
         <v>98.6</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>100</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>8</v>
       </c>
-      <c r="N14">
-        <f>SUM(N9:N13)/5</f>
-        <v>96.6</v>
-      </c>
       <c r="O14">
-        <f>SUM(O9:O13)/5</f>
-        <v>3.4</v>
+        <f t="shared" ref="O14" si="29">SUM(O9:O13)/5</f>
+        <v>99.6</v>
       </c>
       <c r="P14">
-        <f>SUM(P9:P13)/5</f>
+        <f t="shared" ref="P14" si="30">SUM(P9:P13)/5</f>
+        <v>0.4</v>
+      </c>
+      <c r="Q14" s="2">
+        <f t="shared" si="20"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R14">
+        <f t="shared" ref="R14" si="31">SUM(R9:R13)/5</f>
         <v>62.2</v>
       </c>
-      <c r="Q14">
-        <f>SUM(Q9:Q13)/5</f>
+      <c r="S14">
+        <f t="shared" ref="S14" si="32">SUM(S9:S13)/5</f>
         <v>10.8</v>
       </c>
-      <c r="R14">
-        <f>SUM(R9:R13)/5</f>
+      <c r="T14">
+        <f t="shared" ref="T14" si="33">SUM(T9:T13)/5</f>
         <v>309.60000000000002</v>
       </c>
-      <c r="S14">
-        <f>SUM(S9:S13)/5</f>
+      <c r="U14">
+        <f t="shared" ref="U14" si="34">SUM(U9:U13)/5</f>
         <v>41.4</v>
       </c>
-      <c r="T14">
-        <f>SUM(T9:T13)/5</f>
+      <c r="V14">
+        <f t="shared" ref="V14" si="35">SUM(V9:V13)/5</f>
         <v>155</v>
       </c>
-      <c r="U14">
-        <f>SUM(U9:U13)/5</f>
+      <c r="W14">
+        <f t="shared" ref="W14" si="36">SUM(W9:W13)/5</f>
         <v>196</v>
       </c>
-      <c r="V14">
-        <f>SUM(V9:V13)/5</f>
+      <c r="X14">
+        <f t="shared" ref="X14" si="37">SUM(X9:X13)/5</f>
         <v>255.4</v>
       </c>
-      <c r="W14">
+      <c r="Y14">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="D15" s="2"/>
+      <c r="Q15" s="2"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
       <c r="B16">
         <v>441</v>
       </c>
       <c r="C16">
         <v>49</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
+        <f>C16/500</f>
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="E16">
         <v>481</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>7</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>1304</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>565</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>792</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>873</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>1059</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>500</v>
       </c>
-      <c r="N16">
+      <c r="N16" t="s">
+        <v>15</v>
+      </c>
+      <c r="O16">
         <v>478</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>28</v>
       </c>
-      <c r="P16">
+      <c r="Q16" s="2">
+        <f>P16/500</f>
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="R16">
         <v>453</v>
       </c>
-      <c r="Q16">
+      <c r="S16">
         <v>9</v>
       </c>
-      <c r="R16">
+      <c r="T16">
         <v>1423</v>
       </c>
-      <c r="S16">
+      <c r="U16">
         <v>410</v>
       </c>
-      <c r="T16">
+      <c r="V16">
         <v>842</v>
       </c>
-      <c r="U16">
+      <c r="W16">
         <v>902</v>
       </c>
-      <c r="V16">
+      <c r="X16">
         <v>1044</v>
       </c>
-      <c r="W16">
+      <c r="Y16">
         <v>500</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.4">
       <c r="B17">
         <v>445</v>
       </c>
       <c r="C17">
         <v>55</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
+        <f t="shared" ref="D17:D21" si="38">C17/500</f>
+        <v>0.11</v>
+      </c>
+      <c r="E17">
         <v>409</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>8</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>1233</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>368</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>775</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>857</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>974</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>500</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>460</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>40</v>
       </c>
-      <c r="P17">
+      <c r="Q17" s="2">
+        <f t="shared" ref="Q17:Q21" si="39">P17/500</f>
+        <v>0.08</v>
+      </c>
+      <c r="R17">
         <v>475</v>
       </c>
-      <c r="Q17">
+      <c r="S17">
         <v>8</v>
       </c>
-      <c r="R17">
+      <c r="T17">
         <v>1392</v>
       </c>
-      <c r="S17">
+      <c r="U17">
         <v>465</v>
       </c>
-      <c r="T17">
+      <c r="V17">
         <v>808</v>
       </c>
-      <c r="U17">
+      <c r="W17">
         <v>882</v>
       </c>
-      <c r="V17">
+      <c r="X17">
         <v>1103</v>
       </c>
-      <c r="W17">
+      <c r="Y17">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.4">
       <c r="B18">
         <v>456</v>
       </c>
       <c r="C18">
         <v>44</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
+        <f t="shared" si="38"/>
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="E18">
         <v>356</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>9</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>1202</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>371</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>642</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>717</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>910</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>500</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>464</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>36</v>
       </c>
-      <c r="P18">
+      <c r="Q18" s="2">
+        <f t="shared" si="39"/>
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="R18">
         <v>495</v>
       </c>
-      <c r="Q18">
+      <c r="S18">
         <v>7</v>
       </c>
-      <c r="R18">
+      <c r="T18">
         <v>1937</v>
       </c>
-      <c r="S18">
+      <c r="U18">
         <v>372</v>
       </c>
-      <c r="T18">
+      <c r="V18">
         <v>1094</v>
       </c>
-      <c r="U18">
+      <c r="W18">
         <v>1231</v>
       </c>
-      <c r="V18">
+      <c r="X18">
         <v>1567</v>
       </c>
-      <c r="W18">
+      <c r="Y18">
         <v>500</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.4">
       <c r="B19">
         <v>453</v>
       </c>
       <c r="C19">
         <v>47</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
+        <f t="shared" si="38"/>
+        <v>9.4E-2</v>
+      </c>
+      <c r="E19">
         <v>357</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>8</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>1076</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>365</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>555</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>658</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>1033</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>500</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>468</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>32</v>
       </c>
-      <c r="P19">
+      <c r="Q19" s="2">
+        <f t="shared" si="39"/>
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="R19">
         <v>364</v>
       </c>
-      <c r="Q19">
+      <c r="S19">
         <v>8</v>
       </c>
-      <c r="R19">
+      <c r="T19">
         <v>1190</v>
       </c>
-      <c r="S19">
+      <c r="U19">
         <v>360</v>
       </c>
-      <c r="T19">
+      <c r="V19">
         <v>686</v>
       </c>
-      <c r="U19">
+      <c r="W19">
         <v>740</v>
       </c>
-      <c r="V19">
+      <c r="X19">
         <v>1050</v>
       </c>
-      <c r="W19">
+      <c r="Y19">
         <v>500</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.4">
       <c r="B20">
         <v>455</v>
       </c>
       <c r="C20">
         <v>45</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
+        <f t="shared" si="38"/>
+        <v>0.09</v>
+      </c>
+      <c r="E20">
         <v>319</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>7</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>1086</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>297</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>607</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>695</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>860</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>500</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>477</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>23</v>
       </c>
-      <c r="P20">
+      <c r="Q20" s="2">
+        <f t="shared" si="39"/>
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="R20">
         <v>341</v>
       </c>
-      <c r="Q20">
+      <c r="S20">
         <v>9</v>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>1274</v>
       </c>
-      <c r="S20">
+      <c r="U20">
         <v>316</v>
       </c>
-      <c r="T20">
+      <c r="V20">
         <v>639</v>
       </c>
-      <c r="U20">
+      <c r="W20">
         <v>710</v>
       </c>
-      <c r="V20">
+      <c r="X20">
         <v>934</v>
       </c>
-      <c r="W20">
+      <c r="Y20">
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>8</v>
       </c>
       <c r="B21">
-        <f>SUM(B16:B20)/5</f>
+        <f t="shared" ref="B21:J21" si="40">SUM(B16:B20)/5</f>
         <v>450</v>
       </c>
       <c r="C21">
-        <f>SUM(C16:C20)/5</f>
+        <f t="shared" si="40"/>
         <v>48</v>
       </c>
-      <c r="D21">
-        <f>SUM(D16:D20)/5</f>
+      <c r="D21" s="2">
+        <f t="shared" si="38"/>
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="E21">
+        <f t="shared" ref="E21" si="41">SUM(E16:E20)/5</f>
         <v>384.4</v>
       </c>
-      <c r="E21">
-        <f>SUM(E16:E20)/5</f>
+      <c r="F21">
+        <f t="shared" ref="F21" si="42">SUM(F16:F20)/5</f>
         <v>7.8</v>
       </c>
-      <c r="F21">
-        <f>SUM(F16:F20)/5</f>
+      <c r="G21">
+        <f t="shared" ref="G21" si="43">SUM(G16:G20)/5</f>
         <v>1180.2</v>
       </c>
-      <c r="G21">
-        <f>SUM(G16:G20)/5</f>
+      <c r="H21">
+        <f t="shared" ref="H21" si="44">SUM(H16:H20)/5</f>
         <v>393.2</v>
       </c>
-      <c r="H21">
-        <f>SUM(H16:H20)/5</f>
+      <c r="I21">
+        <f t="shared" ref="I21" si="45">SUM(I16:I20)/5</f>
         <v>674.2</v>
       </c>
-      <c r="I21">
-        <f>SUM(I16:I20)/5</f>
+      <c r="J21">
+        <f t="shared" ref="J21" si="46">SUM(J16:J20)/5</f>
         <v>760</v>
       </c>
-      <c r="J21">
-        <f>SUM(J16:J20)/5</f>
+      <c r="K21">
+        <f t="shared" ref="K21" si="47">SUM(K16:K20)/5</f>
         <v>967.2</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>500</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>8</v>
       </c>
-      <c r="N21">
-        <f>SUM(N16:N20)/5</f>
+      <c r="O21">
+        <f t="shared" ref="O21" si="48">SUM(O16:O20)/5</f>
         <v>469.4</v>
       </c>
-      <c r="O21">
-        <f>SUM(O16:O20)/5</f>
+      <c r="P21">
+        <f t="shared" ref="P21" si="49">SUM(P16:P20)/5</f>
         <v>31.8</v>
       </c>
-      <c r="P21">
-        <f>SUM(P16:P20)/5</f>
+      <c r="Q21" s="2">
+        <f t="shared" si="39"/>
+        <v>6.3600000000000004E-2</v>
+      </c>
+      <c r="R21">
+        <f t="shared" ref="R21" si="50">SUM(R16:R20)/5</f>
         <v>425.6</v>
       </c>
-      <c r="Q21">
-        <f>SUM(Q16:Q20)/5</f>
+      <c r="S21">
+        <f t="shared" ref="S21" si="51">SUM(S16:S20)/5</f>
         <v>8.1999999999999993</v>
       </c>
-      <c r="R21">
-        <f>SUM(R16:R20)/5</f>
+      <c r="T21">
+        <f t="shared" ref="T21" si="52">SUM(T16:T20)/5</f>
         <v>1443.2</v>
       </c>
-      <c r="S21">
-        <f>SUM(S16:S20)/5</f>
+      <c r="U21">
+        <f t="shared" ref="U21" si="53">SUM(U16:U20)/5</f>
         <v>384.6</v>
       </c>
-      <c r="T21">
-        <f>SUM(T16:T20)/5</f>
+      <c r="V21">
+        <f t="shared" ref="V21" si="54">SUM(V16:V20)/5</f>
         <v>813.8</v>
       </c>
-      <c r="U21">
-        <f>SUM(U16:U20)/5</f>
+      <c r="W21">
+        <f t="shared" ref="W21" si="55">SUM(W16:W20)/5</f>
         <v>893</v>
       </c>
-      <c r="V21">
-        <f>SUM(V16:V20)/5</f>
+      <c r="X21">
+        <f t="shared" ref="X21" si="56">SUM(X16:X20)/5</f>
         <v>1139.5999999999999</v>
       </c>
-      <c r="W21">
+      <c r="Y21">
         <v>500</v>
       </c>
     </row>
